--- a/screening_results.xlsx
+++ b/screening_results.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen25_all_criteria_no_reason" sheetId="1" r:id="Rb9930a5cfae74b11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen25_all_criteria_reason" sheetId="2" r:id="Ra6a96002941044c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen25_per_criterion_no_reason" sheetId="3" r:id="Rebc3e5f49ff541e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen25_per_criterion_reason" sheetId="4" r:id="R15df39b493434531"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpt_all_criteria_no_reason" sheetId="5" r:id="Rc533a5e85a324926"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpt_all_criteria_reason" sheetId="6" r:id="R1e926c47532e475a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpt_per_criterion_no_reason" sheetId="7" r:id="R8cbd775cfcec49ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpt_per_criterion_reason" sheetId="8" r:id="R0385e4aa7c704daf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen_all_criteria_no_reason" sheetId="9" r:id="Re76fc7baf0974972"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen_all_criteria_reason" sheetId="10" r:id="R5021671be2fc4e98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen_per_criterion_no_reason" sheetId="11" r:id="R60e2f7de9e694748"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen_per_criterion_reason" sheetId="12" r:id="Rcec8ae4d8f3b4a44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Criteria" sheetId="13" r:id="Rbe84598cca8e4594"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpt_initial_criterion_reason" sheetId="14" r:id="R44e67d996ea7448c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen25_all_criteria_no_reason" sheetId="1" r:id="R6d6a277caf684845"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen25_all_criteria_reason" sheetId="2" r:id="Rd7260a1b20f64b6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen25_per_criterion_no_reason" sheetId="3" r:id="R2035e69d7ec04fcc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen25_per_criterion_reason" sheetId="4" r:id="R9762f79b339c4cf0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpt_all_criteria_no_reason" sheetId="5" r:id="Rd4e7ecff923e4a1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpt_all_criteria_reason" sheetId="6" r:id="R28bc138a8d384139"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpt_per_criterion_no_reason" sheetId="7" r:id="R9967b22f796c4ff8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpt_per_criterion_reason" sheetId="8" r:id="Ra22e1f4989cc4f9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen_all_criteria_no_reason" sheetId="9" r:id="R25d930f56f51400f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen_all_criteria_reason" sheetId="10" r:id="Rcb84551d75314740"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen_per_criterion_no_reason" sheetId="11" r:id="R905d0facffc74cd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen_per_criterion_reason" sheetId="12" r:id="R3f6dfe64467b4644"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Criteria" sheetId="13" r:id="R142350fdd3f14134"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpt_initial_criterion_reason" sheetId="14" r:id="R9bab0e5dbc2a4539"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -307,16 +307,16 @@
         <x:v>Journal</x:v>
       </x:c>
       <x:c r="G1" t="str">
-        <x:v>Federico</x:v>
+        <x:v>Reviewer 1</x:v>
       </x:c>
       <x:c r="H1" t="str">
-        <x:v>Linas</x:v>
+        <x:v>Reviewer 2</x:v>
       </x:c>
       <x:c r="I1" t="str">
-        <x:v>Laura</x:v>
+        <x:v>Reviewer 3</x:v>
       </x:c>
       <x:c r="J1" t="str">
-        <x:v>Javad</x:v>
+        <x:v>Reviewer 4</x:v>
       </x:c>
       <x:c r="K1" t="str">
         <x:v>screening_status</x:v>
@@ -2560,16 +2560,16 @@
         <x:v>Journal</x:v>
       </x:c>
       <x:c r="G1" t="str">
-        <x:v>Federico</x:v>
+        <x:v>Reviewer 1</x:v>
       </x:c>
       <x:c r="H1" t="str">
-        <x:v>Linas</x:v>
+        <x:v>Reviewer 2</x:v>
       </x:c>
       <x:c r="I1" t="str">
-        <x:v>Laura</x:v>
+        <x:v>Reviewer 3</x:v>
       </x:c>
       <x:c r="J1" t="str">
-        <x:v>Javad</x:v>
+        <x:v>Reviewer 4</x:v>
       </x:c>
       <x:c r="K1" t="str">
         <x:v>screening_status</x:v>
@@ -4966,16 +4966,16 @@
         <x:v>Journal</x:v>
       </x:c>
       <x:c r="G1" t="str">
-        <x:v>Federico</x:v>
+        <x:v>Reviewer 1</x:v>
       </x:c>
       <x:c r="H1" t="str">
-        <x:v>Linas</x:v>
+        <x:v>Reviewer 2</x:v>
       </x:c>
       <x:c r="I1" t="str">
-        <x:v>Laura</x:v>
+        <x:v>Reviewer 3</x:v>
       </x:c>
       <x:c r="J1" t="str">
-        <x:v>Javad</x:v>
+        <x:v>Reviewer 4</x:v>
       </x:c>
       <x:c r="K1" t="str">
         <x:v>screening_status</x:v>
@@ -8137,16 +8137,16 @@
         <x:v>Journal</x:v>
       </x:c>
       <x:c r="G1" t="str">
-        <x:v>Federico</x:v>
+        <x:v>Reviewer 1</x:v>
       </x:c>
       <x:c r="H1" t="str">
-        <x:v>Linas</x:v>
+        <x:v>Reviewer 2</x:v>
       </x:c>
       <x:c r="I1" t="str">
-        <x:v>Laura</x:v>
+        <x:v>Reviewer 3</x:v>
       </x:c>
       <x:c r="J1" t="str">
-        <x:v>Javad</x:v>
+        <x:v>Reviewer 4</x:v>
       </x:c>
       <x:c r="K1" t="str">
         <x:v>screening_status</x:v>
@@ -11825,16 +11825,16 @@
         <x:v>Journal</x:v>
       </x:c>
       <x:c r="G1" t="str">
-        <x:v>Federico</x:v>
+        <x:v>Reviewer 1</x:v>
       </x:c>
       <x:c r="H1" t="str">
-        <x:v>Linas</x:v>
+        <x:v>Reviewer 2</x:v>
       </x:c>
       <x:c r="I1" t="str">
-        <x:v>Laura</x:v>
+        <x:v>Reviewer 3</x:v>
       </x:c>
       <x:c r="J1" t="str">
-        <x:v>Javad</x:v>
+        <x:v>Reviewer 4</x:v>
       </x:c>
       <x:c r="K1" t="str">
         <x:v>screening_status</x:v>
@@ -15429,7 +15429,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R396fc3cd52254a2c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f712fb286e544dd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15458,16 +15458,16 @@
         <x:v>Journal</x:v>
       </x:c>
       <x:c r="G1" t="str">
-        <x:v>Federico</x:v>
+        <x:v>Reviewer 1</x:v>
       </x:c>
       <x:c r="H1" t="str">
-        <x:v>Linas</x:v>
+        <x:v>Reviewer 2</x:v>
       </x:c>
       <x:c r="I1" t="str">
-        <x:v>Laura</x:v>
+        <x:v>Reviewer 3</x:v>
       </x:c>
       <x:c r="J1" t="str">
-        <x:v>Javad</x:v>
+        <x:v>Reviewer 4</x:v>
       </x:c>
       <x:c r="K1" t="str">
         <x:v>screening_status</x:v>
@@ -17864,16 +17864,16 @@
         <x:v>Journal</x:v>
       </x:c>
       <x:c r="G1" t="str">
-        <x:v>Federico</x:v>
+        <x:v>Reviewer 1</x:v>
       </x:c>
       <x:c r="H1" t="str">
-        <x:v>Linas</x:v>
+        <x:v>Reviewer 2</x:v>
       </x:c>
       <x:c r="I1" t="str">
-        <x:v>Laura</x:v>
+        <x:v>Reviewer 3</x:v>
       </x:c>
       <x:c r="J1" t="str">
-        <x:v>Javad</x:v>
+        <x:v>Reviewer 4</x:v>
       </x:c>
       <x:c r="K1" t="str">
         <x:v>screening_status</x:v>
@@ -21035,16 +21035,16 @@
         <x:v>Journal</x:v>
       </x:c>
       <x:c r="G1" t="str">
-        <x:v>Federico</x:v>
+        <x:v>Reviewer 1</x:v>
       </x:c>
       <x:c r="H1" t="str">
-        <x:v>Linas</x:v>
+        <x:v>Reviewer 2</x:v>
       </x:c>
       <x:c r="I1" t="str">
-        <x:v>Laura</x:v>
+        <x:v>Reviewer 3</x:v>
       </x:c>
       <x:c r="J1" t="str">
-        <x:v>Javad</x:v>
+        <x:v>Reviewer 4</x:v>
       </x:c>
       <x:c r="K1" t="str">
         <x:v>screening_status</x:v>
@@ -24665,16 +24665,16 @@
         <x:v>Journal</x:v>
       </x:c>
       <x:c r="G1" t="str">
-        <x:v>Federico</x:v>
+        <x:v>Reviewer 1</x:v>
       </x:c>
       <x:c r="H1" t="str">
-        <x:v>Linas</x:v>
+        <x:v>Reviewer 2</x:v>
       </x:c>
       <x:c r="I1" t="str">
-        <x:v>Laura</x:v>
+        <x:v>Reviewer 3</x:v>
       </x:c>
       <x:c r="J1" t="str">
-        <x:v>Javad</x:v>
+        <x:v>Reviewer 4</x:v>
       </x:c>
       <x:c r="K1" t="str">
         <x:v>screening_status</x:v>
@@ -26918,16 +26918,16 @@
         <x:v>Journal</x:v>
       </x:c>
       <x:c r="G1" t="str">
-        <x:v>Federico</x:v>
+        <x:v>Reviewer 1</x:v>
       </x:c>
       <x:c r="H1" t="str">
-        <x:v>Linas</x:v>
+        <x:v>Reviewer 2</x:v>
       </x:c>
       <x:c r="I1" t="str">
-        <x:v>Laura</x:v>
+        <x:v>Reviewer 3</x:v>
       </x:c>
       <x:c r="J1" t="str">
-        <x:v>Javad</x:v>
+        <x:v>Reviewer 4</x:v>
       </x:c>
       <x:c r="K1" t="str">
         <x:v>screening_status</x:v>
@@ -29324,16 +29324,16 @@
         <x:v>Journal</x:v>
       </x:c>
       <x:c r="G1" t="str">
-        <x:v>Federico</x:v>
+        <x:v>Reviewer 1</x:v>
       </x:c>
       <x:c r="H1" t="str">
-        <x:v>Linas</x:v>
+        <x:v>Reviewer 2</x:v>
       </x:c>
       <x:c r="I1" t="str">
-        <x:v>Laura</x:v>
+        <x:v>Reviewer 3</x:v>
       </x:c>
       <x:c r="J1" t="str">
-        <x:v>Javad</x:v>
+        <x:v>Reviewer 4</x:v>
       </x:c>
       <x:c r="K1" t="str">
         <x:v>screening_status</x:v>
@@ -32495,16 +32495,16 @@
         <x:v>Journal</x:v>
       </x:c>
       <x:c r="G1" t="str">
-        <x:v>Federico</x:v>
+        <x:v>Reviewer 1</x:v>
       </x:c>
       <x:c r="H1" t="str">
-        <x:v>Linas</x:v>
+        <x:v>Reviewer 2</x:v>
       </x:c>
       <x:c r="I1" t="str">
-        <x:v>Laura</x:v>
+        <x:v>Reviewer 3</x:v>
       </x:c>
       <x:c r="J1" t="str">
-        <x:v>Javad</x:v>
+        <x:v>Reviewer 4</x:v>
       </x:c>
       <x:c r="K1" t="str">
         <x:v>screening_status</x:v>
@@ -36125,16 +36125,16 @@
         <x:v>Journal</x:v>
       </x:c>
       <x:c r="G1" t="str">
-        <x:v>Federico</x:v>
+        <x:v>Reviewer 1</x:v>
       </x:c>
       <x:c r="H1" t="str">
-        <x:v>Linas</x:v>
+        <x:v>Reviewer 2</x:v>
       </x:c>
       <x:c r="I1" t="str">
-        <x:v>Laura</x:v>
+        <x:v>Reviewer 3</x:v>
       </x:c>
       <x:c r="J1" t="str">
-        <x:v>Javad</x:v>
+        <x:v>Reviewer 4</x:v>
       </x:c>
       <x:c r="K1" t="str">
         <x:v>screening_status</x:v>

--- a/screening_results.xlsx
+++ b/screening_results.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen25_all_criteria_no_reason" sheetId="1" r:id="R6d6a277caf684845"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen25_all_criteria_reason" sheetId="2" r:id="Rd7260a1b20f64b6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen25_per_criterion_no_reason" sheetId="3" r:id="R2035e69d7ec04fcc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen25_per_criterion_reason" sheetId="4" r:id="R9762f79b339c4cf0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpt_all_criteria_no_reason" sheetId="5" r:id="Rd4e7ecff923e4a1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpt_all_criteria_reason" sheetId="6" r:id="R28bc138a8d384139"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpt_per_criterion_no_reason" sheetId="7" r:id="R9967b22f796c4ff8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpt_per_criterion_reason" sheetId="8" r:id="Ra22e1f4989cc4f9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen_all_criteria_no_reason" sheetId="9" r:id="R25d930f56f51400f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen_all_criteria_reason" sheetId="10" r:id="Rcb84551d75314740"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen_per_criterion_no_reason" sheetId="11" r:id="R905d0facffc74cd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen_per_criterion_reason" sheetId="12" r:id="R3f6dfe64467b4644"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Criteria" sheetId="13" r:id="R142350fdd3f14134"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpt_initial_criterion_reason" sheetId="14" r:id="R9bab0e5dbc2a4539"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen25_all_criteria_no_reason" sheetId="1" r:id="R3f396b1c34e14807"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen25_all_criteria_reason" sheetId="2" r:id="R2a4e43cb3e2f4d87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen25_per_criterion_no_reason" sheetId="3" r:id="R32b271ce86d6401c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen25_per_criterion_reason" sheetId="4" r:id="Rc220c8d405d74243"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpt_all_criteria_no_reason" sheetId="5" r:id="Rbe8e4370219545ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpt_all_criteria_reason" sheetId="6" r:id="R4bc59eb46f5e4d1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpt_per_criterion_no_reason" sheetId="7" r:id="R4cb70f1f48ad41c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpt_per_criterion_reason" sheetId="8" r:id="Rc0de0f492b994dc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen_all_criteria_no_reason" sheetId="9" r:id="R66c4bea53b21403b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen_all_criteria_reason" sheetId="10" r:id="R08304b5e1c4a4b52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen_per_criterion_no_reason" sheetId="11" r:id="Rb148b9e113f948b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="qwen_per_criterion_reason" sheetId="12" r:id="R4353c4591a1647db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Criteria" sheetId="13" r:id="Rab3bfaa4cf544b06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpt_initial_criterion_reason" sheetId="14" r:id="Rd37fd55ce1094f0c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -59,37 +59,6 @@
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Gpt818RunTable" displayName="Gpt818RunTable" ref="A1:W51" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="23">
-    <x:tableColumn id="1" name="row"/>
-    <x:tableColumn id="2" name="title"/>
-    <x:tableColumn id="3" name="abstract"/>
-    <x:tableColumn id="4" name="Authors"/>
-    <x:tableColumn id="5" name="Year"/>
-    <x:tableColumn id="6" name="Journal"/>
-    <x:tableColumn id="7" name="Federico"/>
-    <x:tableColumn id="8" name="Linas"/>
-    <x:tableColumn id="9" name="Laura"/>
-    <x:tableColumn id="10" name="Javad"/>
-    <x:tableColumn id="11" name="screening_status"/>
-    <x:tableColumn id="12" name="decision"/>
-    <x:tableColumn id="13" name="reason"/>
-    <x:tableColumn id="14" name="blocking_criteria"/>
-    <x:tableColumn id="15" name="Active interaction (decision)"/>
-    <x:tableColumn id="16" name="Active interaction (finding)"/>
-    <x:tableColumn id="17" name="Active interaction (reason)"/>
-    <x:tableColumn id="18" name="Focus (decision)"/>
-    <x:tableColumn id="19" name="Focus (finding)"/>
-    <x:tableColumn id="20" name="Focus (reason)"/>
-    <x:tableColumn id="21" name="Digital Medium (decision)"/>
-    <x:tableColumn id="22" name="Digital Medium (finding)"/>
-    <x:tableColumn id="23" name="Digital Medium (reason)"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
-</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15428,9 +15397,6 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f712fb286e544dd"/>
-  </x:tableParts>
 </x:worksheet>
 </file>
 
